--- a/reports/Test-Cases-saucedemo.xlsx
+++ b/reports/Test-Cases-saucedemo.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
   <si>
     <t>FEATURE</t>
   </si>
@@ -50,7 +50,7 @@
     <t>SAUCE-001</t>
   </si>
   <si>
-    <t>2026-09-21 12:41:15</t>
+    <t>2026-09-21 13:20:27</t>
   </si>
   <si>
     <t>PASS</t>
@@ -120,7 +120,7 @@
     <t>User authenticated; session cookie set</t>
   </si>
   <si>
-    <t>Passed in 1.7s on chromium.</t>
+    <t>Passed in 1.9s on chromium.</t>
   </si>
   <si>
     <t>SAUCE-001-NEG-01</t>
@@ -149,6 +149,9 @@
   </si>
   <si>
     <t>No session established</t>
+  </si>
+  <si>
+    <t>Passed in 1.5s on chromium.</t>
   </si>
 </sst>
 </file>
@@ -808,7 +811,7 @@
         <v>42</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>

--- a/reports/Test-Cases-saucedemo.xlsx
+++ b/reports/Test-Cases-saucedemo.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>FEATURE</t>
   </si>
@@ -50,10 +50,10 @@
     <t>SAUCE-001</t>
   </si>
   <si>
-    <t>2026-09-21 13:20:27</t>
-  </si>
-  <si>
-    <t>PASS</t>
+    <t>never</t>
+  </si>
+  <si>
+    <t>NOT RUN</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -120,7 +120,7 @@
     <t>User authenticated; session cookie set</t>
   </si>
   <si>
-    <t>Passed in 1.9s on chromium.</t>
+    <t>No run data — execute the suite to capture the actual result.</t>
   </si>
   <si>
     <t>SAUCE-001-NEG-01</t>
@@ -149,9 +149,6 @@
   </si>
   <si>
     <t>No session established</t>
-  </si>
-  <si>
-    <t>Passed in 1.5s on chromium.</t>
   </si>
 </sst>
 </file>
@@ -178,7 +175,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF155724"/>
+      <color rgb="FF856404"/>
       <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
@@ -202,7 +199,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
+        <fgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -651,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -683,7 +680,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" s="4">
         <v>0</v>
@@ -811,7 +808,7 @@
         <v>42</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>

--- a/reports/Test-Cases-saucedemo.xlsx
+++ b/reports/Test-Cases-saucedemo.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
   <si>
     <t>FEATURE</t>
   </si>
@@ -50,10 +50,10 @@
     <t>SAUCE-001</t>
   </si>
   <si>
-    <t>never</t>
-  </si>
-  <si>
-    <t>NOT RUN</t>
+    <t>2026-09-22 15:52:14</t>
+  </si>
+  <si>
+    <t>PASS</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -120,7 +120,7 @@
     <t>User authenticated; session cookie set</t>
   </si>
   <si>
-    <t>No run data — execute the suite to capture the actual result.</t>
+    <t>Passed in 2.1s on chromium.</t>
   </si>
   <si>
     <t>SAUCE-001-NEG-01</t>
@@ -149,6 +149,9 @@
   </si>
   <si>
     <t>No session established</t>
+  </si>
+  <si>
+    <t>Passed in 1.5s on chromium.</t>
   </si>
 </sst>
 </file>
@@ -175,7 +178,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF856404"/>
+      <color rgb="FF155724"/>
       <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
@@ -199,7 +202,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
+        <fgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -648,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -680,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="4">
         <v>0</v>
@@ -808,7 +811,7 @@
         <v>42</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>

--- a/reports/Test-Cases-saucedemo.xlsx
+++ b/reports/Test-Cases-saucedemo.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>FEATURE</t>
   </si>
@@ -50,7 +50,7 @@
     <t>SAUCE-001</t>
   </si>
   <si>
-    <t>2026-09-22 15:52:14</t>
+    <t>2026-09-22 16:00:06</t>
   </si>
   <si>
     <t>PASS</t>
@@ -120,7 +120,7 @@
     <t>User authenticated; session cookie set</t>
   </si>
   <si>
-    <t>Passed in 2.1s on chromium.</t>
+    <t>Passed in 1.6s on chromium.</t>
   </si>
   <si>
     <t>SAUCE-001-NEG-01</t>
@@ -149,9 +149,6 @@
   </si>
   <si>
     <t>No session established</t>
-  </si>
-  <si>
-    <t>Passed in 1.5s on chromium.</t>
   </si>
 </sst>
 </file>
@@ -811,7 +808,7 @@
         <v>42</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>

--- a/reports/Test-Cases-saucedemo.xlsx
+++ b/reports/Test-Cases-saucedemo.xlsx
@@ -50,7 +50,7 @@
     <t>SAUCE-001</t>
   </si>
   <si>
-    <t>2026-09-22 16:00:06</t>
+    <t>2026-09-22 16:03:07</t>
   </si>
   <si>
     <t>PASS</t>
@@ -120,7 +120,7 @@
     <t>User authenticated; session cookie set</t>
   </si>
   <si>
-    <t>Passed in 1.6s on chromium.</t>
+    <t>Passed in 2.1s on chromium.</t>
   </si>
   <si>
     <t>SAUCE-001-NEG-01</t>

--- a/reports/Test-Cases-saucedemo.xlsx
+++ b/reports/Test-Cases-saucedemo.xlsx
@@ -50,10 +50,10 @@
     <t>SAUCE-001</t>
   </si>
   <si>
-    <t>2026-09-22 16:03:07</t>
-  </si>
-  <si>
-    <t>PASS</t>
+    <t>never</t>
+  </si>
+  <si>
+    <t>NOT RUN</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -120,7 +120,7 @@
     <t>User authenticated; session cookie set</t>
   </si>
   <si>
-    <t>Passed in 2.1s on chromium.</t>
+    <t>No run data — execute the suite to capture the actual result.</t>
   </si>
   <si>
     <t>SAUCE-001-NEG-01</t>
@@ -175,7 +175,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF155724"/>
+      <color rgb="FF856404"/>
       <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
@@ -199,7 +199,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
+        <fgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -680,7 +680,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" s="4">
         <v>0</v>

--- a/reports/Test-Cases-saucedemo.xlsx
+++ b/reports/Test-Cases-saucedemo.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
   <si>
     <t>FEATURE</t>
   </si>
@@ -50,10 +50,10 @@
     <t>SAUCE-001</t>
   </si>
   <si>
-    <t>never</t>
-  </si>
-  <si>
-    <t>NOT RUN</t>
+    <t>2026-09-22 17:51:47</t>
+  </si>
+  <si>
+    <t>PASS</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -120,7 +120,7 @@
     <t>User authenticated; session cookie set</t>
   </si>
   <si>
-    <t>No run data — execute the suite to capture the actual result.</t>
+    <t>Passed in 3.4s on chromium.</t>
   </si>
   <si>
     <t>SAUCE-001-NEG-01</t>
@@ -149,6 +149,9 @@
   </si>
   <si>
     <t>No session established</t>
+  </si>
+  <si>
+    <t>Passed in 1.6s on chromium.</t>
   </si>
 </sst>
 </file>
@@ -175,7 +178,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF856404"/>
+      <color rgb="FF155724"/>
       <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
@@ -199,7 +202,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
+        <fgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -648,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -680,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="4">
         <v>0</v>
@@ -808,7 +811,7 @@
         <v>42</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
